--- a/processed_data/hard_data_exports/hunt_tables/2026/2026_ELK_ANTLERLESS.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/2026_ELK_ANTLERLESS.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="135" windowWidth="28800" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_elk_antlerless" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026_elk_antlerless" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_elk_antlerless'!$A$3:$J$207</definedName>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J207"/>
+  <dimension ref="A1:N207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -615,6 +615,26 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Prior Year</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Success (Prior Year %)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Average Harvest Age (Prior Year)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Average Days Hunted (Prior Year)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -667,6 +687,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -719,6 +753,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -771,6 +819,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -823,6 +885,20 @@
           <t>70</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -875,6 +951,20 @@
           <t>70</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -927,6 +1017,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -979,6 +1083,20 @@
           <t>60</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>69.8</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1031,6 +1149,20 @@
           <t>120</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>37.2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1083,6 +1215,20 @@
           <t>230</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1135,6 +1281,20 @@
           <t>300</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>34.9</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1187,6 +1347,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>35.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -1239,6 +1413,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1291,6 +1479,20 @@
           <t>120</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -1343,6 +1545,20 @@
           <t>350</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1395,6 +1611,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>31.7</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -1447,6 +1677,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>48.9</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -1499,6 +1743,20 @@
           <t>125</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -1551,6 +1809,20 @@
           <t>125</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -1603,6 +1875,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -1655,6 +1941,20 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -1707,6 +2007,20 @@
           <t>150</t>
         </is>
       </c>
+      <c r="K24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>35.2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -1759,6 +2073,20 @@
           <t>35</t>
         </is>
       </c>
+      <c r="K25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -1811,6 +2139,20 @@
           <t>75</t>
         </is>
       </c>
+      <c r="K26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -1863,6 +2205,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -1915,6 +2271,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -1967,6 +2337,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>32.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -2019,6 +2403,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
@@ -2071,6 +2469,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -2123,6 +2535,20 @@
           <t>75</t>
         </is>
       </c>
+      <c r="K32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
@@ -2175,6 +2601,20 @@
           <t>75</t>
         </is>
       </c>
+      <c r="K33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -2227,6 +2667,20 @@
           <t>35</t>
         </is>
       </c>
+      <c r="K34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
@@ -2279,6 +2733,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K35" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -2331,6 +2799,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -2383,6 +2865,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K37" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>80.9</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -2435,6 +2931,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
@@ -2487,6 +2997,20 @@
           <t>270</t>
         </is>
       </c>
+      <c r="K39" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>36.8</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -2539,6 +3063,20 @@
           <t>65</t>
         </is>
       </c>
+      <c r="K40" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
@@ -2591,6 +3129,20 @@
           <t>60</t>
         </is>
       </c>
+      <c r="K41" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -2643,6 +3195,20 @@
           <t>125</t>
         </is>
       </c>
+      <c r="K42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
@@ -2695,6 +3261,20 @@
           <t>125</t>
         </is>
       </c>
+      <c r="K43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -2747,6 +3327,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
@@ -2799,6 +3393,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K45" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -2851,6 +3459,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K46" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
@@ -2903,6 +3525,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -2955,6 +3591,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>24.4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
@@ -3007,6 +3657,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K49" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>47.1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -3059,6 +3723,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K50" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
@@ -3111,6 +3789,20 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -3163,6 +3855,20 @@
           <t>45</t>
         </is>
       </c>
+      <c r="K52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
@@ -3215,6 +3921,20 @@
           <t>35</t>
         </is>
       </c>
+      <c r="K53" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -3267,6 +3987,20 @@
           <t>55</t>
         </is>
       </c>
+      <c r="K54" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
@@ -3319,6 +4053,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K55" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -3371,6 +4119,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
@@ -3423,6 +4185,20 @@
           <t>220</t>
         </is>
       </c>
+      <c r="K57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -3475,6 +4251,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K58" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
@@ -3527,6 +4317,20 @@
           <t>12</t>
         </is>
       </c>
+      <c r="K59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -3579,6 +4383,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K60" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
@@ -3631,6 +4449,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K61" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -3683,6 +4515,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K62" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
@@ -3735,6 +4581,20 @@
           <t>12</t>
         </is>
       </c>
+      <c r="K63" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -3787,6 +4647,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K64" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
@@ -3839,6 +4713,20 @@
           <t>425</t>
         </is>
       </c>
+      <c r="K65" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -3891,6 +4779,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K66" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
@@ -3943,6 +4845,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -3995,6 +4911,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K68" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
@@ -4047,6 +4977,20 @@
           <t>60</t>
         </is>
       </c>
+      <c r="K69" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -4099,6 +5043,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K70" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>63.2</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
@@ -4151,6 +5109,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -4203,6 +5175,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K72" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
@@ -4255,6 +5241,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K73" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -4307,6 +5307,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K74" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
@@ -4359,6 +5373,20 @@
           <t>24</t>
         </is>
       </c>
+      <c r="K75" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -4411,6 +5439,20 @@
           <t>12</t>
         </is>
       </c>
+      <c r="K76" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
@@ -4463,6 +5505,20 @@
           <t>12</t>
         </is>
       </c>
+      <c r="K77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -4515,6 +5571,20 @@
           <t>21</t>
         </is>
       </c>
+      <c r="K78" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>97.1</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
@@ -4567,6 +5637,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K79" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -4619,6 +5703,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K80" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
@@ -4671,6 +5769,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K81" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -4723,6 +5835,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K82" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
@@ -4775,6 +5901,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K83" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -4827,6 +5967,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K84" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
@@ -4879,6 +6033,20 @@
           <t>21</t>
         </is>
       </c>
+      <c r="K85" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -4931,6 +6099,20 @@
           <t>35</t>
         </is>
       </c>
+      <c r="K86" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
@@ -4983,6 +6165,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K87" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -5035,6 +6231,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K88" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
@@ -5087,6 +6297,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K89" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -5139,6 +6363,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K90" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
@@ -5191,6 +6429,20 @@
           <t>14</t>
         </is>
       </c>
+      <c r="K91" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
@@ -5243,6 +6495,20 @@
           <t>19</t>
         </is>
       </c>
+      <c r="K92" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
@@ -5295,6 +6561,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K93" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -5347,6 +6627,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K94" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>92.9</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
@@ -5399,6 +6693,20 @@
           <t>16</t>
         </is>
       </c>
+      <c r="K95" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>46.7</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -5451,6 +6759,20 @@
           <t>12</t>
         </is>
       </c>
+      <c r="K96" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
@@ -5503,6 +6825,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K97" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>63.2</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
@@ -5555,6 +6891,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K98" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
@@ -5607,6 +6957,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K99" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="24" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
@@ -5659,6 +7023,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K100" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
@@ -5711,6 +7089,20 @@
           <t>60</t>
         </is>
       </c>
+      <c r="K101" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>71.4</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
@@ -5763,6 +7155,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K102" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
@@ -5813,6 +7219,20 @@
       <c r="J103" s="8" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>1.9</t>
         </is>
       </c>
     </row>
@@ -5855,6 +7275,20 @@
       <c r="H104" s="6" t="inlineStr"/>
       <c r="I104" s="6" t="inlineStr"/>
       <c r="J104" s="6" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
@@ -5907,6 +7341,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K105" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
@@ -5959,6 +7407,20 @@
           <t>425</t>
         </is>
       </c>
+      <c r="K106" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
@@ -6011,6 +7473,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K107" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
@@ -6063,6 +7539,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
@@ -6115,6 +7605,20 @@
           <t>75</t>
         </is>
       </c>
+      <c r="K109" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
@@ -6167,6 +7671,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
@@ -6219,6 +7737,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
@@ -6271,6 +7803,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
@@ -6323,6 +7869,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
@@ -6375,6 +7935,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K114" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="24" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
@@ -6427,6 +8001,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
@@ -6479,6 +8067,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
@@ -6531,6 +8133,20 @@
           <t>275</t>
         </is>
       </c>
+      <c r="K117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>45.9</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
@@ -6583,6 +8199,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
@@ -6633,6 +8263,20 @@
       <c r="J119" s="8" t="inlineStr">
         <is>
           <t>150</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -6675,6 +8319,12 @@
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="6" t="inlineStr"/>
       <c r="J120" s="6" t="inlineStr"/>
+      <c r="K120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
@@ -6715,6 +8365,20 @@
       <c r="H121" s="8" t="inlineStr"/>
       <c r="I121" s="8" t="inlineStr"/>
       <c r="J121" s="8" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
@@ -6767,6 +8431,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
@@ -6819,6 +8497,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K123" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>37.9</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
@@ -6871,6 +8563,20 @@
           <t>130</t>
         </is>
       </c>
+      <c r="K124" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="24" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
@@ -6923,6 +8629,20 @@
           <t>163</t>
         </is>
       </c>
+      <c r="K125" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>78.1</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
@@ -6975,6 +8695,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
@@ -7027,6 +8761,20 @@
           <t>75</t>
         </is>
       </c>
+      <c r="K127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="24" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
@@ -7079,6 +8827,20 @@
           <t>160</t>
         </is>
       </c>
+      <c r="K128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="24" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
@@ -7131,6 +8893,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>32.5</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="24" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
@@ -7183,6 +8959,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
@@ -7235,6 +9025,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>43.8</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="24" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
@@ -7287,6 +9091,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K132" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="24" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
@@ -7339,6 +9157,20 @@
           <t>150</t>
         </is>
       </c>
+      <c r="K133" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
@@ -7391,6 +9223,20 @@
           <t>175</t>
         </is>
       </c>
+      <c r="K134" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="24" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
@@ -7443,6 +9289,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K135" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>34.9</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="24" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
@@ -7495,6 +9355,20 @@
           <t>150</t>
         </is>
       </c>
+      <c r="K136" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>47.7</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="24" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
@@ -7547,6 +9421,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="24" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
@@ -7599,6 +9487,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K138" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
@@ -7651,6 +9553,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="24" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
@@ -7703,6 +9619,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="24" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
@@ -7755,6 +9685,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="24" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
@@ -7807,6 +9751,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="24" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
@@ -7859,6 +9817,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="24" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
@@ -7911,6 +9883,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K144" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="24" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
@@ -7961,6 +9947,20 @@
       <c r="J145" s="8" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>2.7</t>
         </is>
       </c>
     </row>
@@ -8003,6 +10003,12 @@
       <c r="H146" s="6" t="inlineStr"/>
       <c r="I146" s="6" t="inlineStr"/>
       <c r="J146" s="6" t="inlineStr"/>
+      <c r="K146" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147" ht="24" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
@@ -8055,6 +10061,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="24" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
@@ -8107,6 +10127,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="24" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
@@ -8159,6 +10193,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="32" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
@@ -8211,6 +10259,20 @@
           <t>35</t>
         </is>
       </c>
+      <c r="K150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="24" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
@@ -8263,6 +10325,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K151" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="24" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
@@ -8315,6 +10391,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="24" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
@@ -8367,6 +10457,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="24" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
@@ -8419,6 +10523,20 @@
           <t>90</t>
         </is>
       </c>
+      <c r="K154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="24" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
@@ -8471,6 +10589,20 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="24" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
@@ -8521,6 +10653,20 @@
       <c r="J156" s="6" t="inlineStr">
         <is>
           <t>200</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>30.1</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>5.4</t>
         </is>
       </c>
     </row>
@@ -8563,6 +10709,20 @@
       <c r="H157" s="8" t="inlineStr"/>
       <c r="I157" s="8" t="inlineStr"/>
       <c r="J157" s="8" t="inlineStr"/>
+      <c r="K157" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="32" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
@@ -8603,6 +10763,20 @@
       <c r="H158" s="6" t="inlineStr"/>
       <c r="I158" s="6" t="inlineStr"/>
       <c r="J158" s="6" t="inlineStr"/>
+      <c r="K158" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="24" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
@@ -8655,6 +10829,20 @@
           <t>150</t>
         </is>
       </c>
+      <c r="K159" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="24" customHeight="1">
       <c r="A160" s="5" t="inlineStr">
@@ -8707,6 +10895,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K160" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>82.6</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="24" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
@@ -8759,6 +10961,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K161" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="24" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
@@ -8811,6 +11027,20 @@
           <t>45</t>
         </is>
       </c>
+      <c r="K162" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>36.7</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="24" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
@@ -8863,6 +11093,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K163" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="24" customHeight="1">
       <c r="A164" s="5" t="inlineStr">
@@ -8915,6 +11159,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K164" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="24" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
@@ -8967,6 +11225,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K165" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="24" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
@@ -9019,6 +11291,20 @@
           <t>175</t>
         </is>
       </c>
+      <c r="K166" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="24" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
@@ -9071,6 +11357,20 @@
           <t>75</t>
         </is>
       </c>
+      <c r="K167" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="24" customHeight="1">
       <c r="A168" s="5" t="inlineStr">
@@ -9123,6 +11423,12 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K168" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169" ht="24" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
@@ -9175,6 +11481,20 @@
           <t>35</t>
         </is>
       </c>
+      <c r="K169" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="24" customHeight="1">
       <c r="A170" s="5" t="inlineStr">
@@ -9227,6 +11547,20 @@
           <t>35</t>
         </is>
       </c>
+      <c r="K170" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="24" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
@@ -9277,6 +11611,20 @@
       <c r="J171" s="8" t="inlineStr">
         <is>
           <t>35</t>
+        </is>
+      </c>
+      <c r="K171" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>2.2</t>
         </is>
       </c>
     </row>
@@ -9319,6 +11667,20 @@
       <c r="H172" s="6" t="inlineStr"/>
       <c r="I172" s="6" t="inlineStr"/>
       <c r="J172" s="6" t="inlineStr"/>
+      <c r="K172" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="54" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
@@ -9359,6 +11721,20 @@
       <c r="H173" s="8" t="inlineStr"/>
       <c r="I173" s="8" t="inlineStr"/>
       <c r="J173" s="8" t="inlineStr"/>
+      <c r="K173" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="24" customHeight="1">
       <c r="A174" s="5" t="inlineStr">
@@ -9403,6 +11779,20 @@
           <t>600</t>
         </is>
       </c>
+      <c r="K174" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="24" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
@@ -9447,6 +11837,20 @@
           <t>500</t>
         </is>
       </c>
+      <c r="K175" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="24" customHeight="1">
       <c r="A176" s="5" t="inlineStr">
@@ -9491,6 +11895,20 @@
           <t>600</t>
         </is>
       </c>
+      <c r="K176" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>35.4</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="24" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
@@ -9535,6 +11953,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K177" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="24" customHeight="1">
       <c r="A178" s="5" t="inlineStr">
@@ -9579,6 +12011,20 @@
           <t>2000</t>
         </is>
       </c>
+      <c r="K178" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>46.7</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="24" customHeight="1">
       <c r="A179" s="7" t="inlineStr">
@@ -9623,6 +12069,20 @@
           <t>250</t>
         </is>
       </c>
+      <c r="K179" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="24" customHeight="1">
       <c r="A180" s="5" t="inlineStr">
@@ -9667,6 +12127,20 @@
           <t>70</t>
         </is>
       </c>
+      <c r="K180" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>27.8</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="24" customHeight="1">
       <c r="A181" s="7" t="inlineStr">
@@ -9711,6 +12185,20 @@
           <t>50</t>
         </is>
       </c>
+      <c r="K181" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="24" customHeight="1">
       <c r="A182" s="5" t="inlineStr">
@@ -9755,6 +12243,20 @@
           <t>300</t>
         </is>
       </c>
+      <c r="K182" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>41.6</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="24" customHeight="1">
       <c r="A183" s="7" t="inlineStr">
@@ -9799,6 +12301,20 @@
           <t>400</t>
         </is>
       </c>
+      <c r="K183" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>53.1</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="24" customHeight="1">
       <c r="A184" s="5" t="inlineStr">
@@ -9843,6 +12359,20 @@
           <t>2000</t>
         </is>
       </c>
+      <c r="K184" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>37.8</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="24" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
@@ -9887,6 +12417,20 @@
           <t>400</t>
         </is>
       </c>
+      <c r="K185" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>40.9</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="24" customHeight="1">
       <c r="A186" s="5" t="inlineStr">
@@ -9931,6 +12475,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K186" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="24" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
@@ -9975,6 +12533,20 @@
           <t>275</t>
         </is>
       </c>
+      <c r="K187" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>36.7</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="24" customHeight="1">
       <c r="A188" s="5" t="inlineStr">
@@ -10019,6 +12591,20 @@
           <t>75</t>
         </is>
       </c>
+      <c r="K188" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="24" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
@@ -10063,6 +12649,20 @@
           <t>75</t>
         </is>
       </c>
+      <c r="K189" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="24" customHeight="1">
       <c r="A190" s="5" t="inlineStr">
@@ -10107,6 +12707,20 @@
           <t>60</t>
         </is>
       </c>
+      <c r="K190" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="24" customHeight="1">
       <c r="A191" s="7" t="inlineStr">
@@ -10151,6 +12765,20 @@
           <t>320</t>
         </is>
       </c>
+      <c r="K191" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="24" customHeight="1">
       <c r="A192" s="5" t="inlineStr">
@@ -10195,6 +12823,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K192" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="24" customHeight="1">
       <c r="A193" s="7" t="inlineStr">
@@ -10239,6 +12881,20 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K193" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="24" customHeight="1">
       <c r="A194" s="5" t="inlineStr">
@@ -10283,6 +12939,20 @@
           <t>300</t>
         </is>
       </c>
+      <c r="K194" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="24" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
@@ -10327,6 +12997,20 @@
           <t>450</t>
         </is>
       </c>
+      <c r="K195" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="24" customHeight="1">
       <c r="A196" s="5" t="inlineStr">
@@ -10371,6 +13055,20 @@
           <t>150</t>
         </is>
       </c>
+      <c r="K196" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>34.7</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="24" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
@@ -10415,6 +13113,20 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K197" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="24" customHeight="1">
       <c r="A198" s="5" t="inlineStr">
@@ -10467,6 +13179,20 @@
           <t>250</t>
         </is>
       </c>
+      <c r="K198" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="24" customHeight="1">
       <c r="A199" s="7" t="inlineStr">
@@ -10519,6 +13245,20 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K199" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="24" customHeight="1">
       <c r="A200" s="5" t="inlineStr">
@@ -10571,6 +13311,20 @@
           <t>60</t>
         </is>
       </c>
+      <c r="K200" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>91.4</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="24" customHeight="1">
       <c r="A201" s="7" t="inlineStr">
@@ -10623,6 +13377,20 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K201" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="24" customHeight="1">
       <c r="A202" s="5" t="inlineStr">
@@ -10673,6 +13441,20 @@
       <c r="J202" s="6" t="inlineStr">
         <is>
           <t>1200</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>5.8</t>
         </is>
       </c>
     </row>
@@ -10719,6 +13501,20 @@
           <t>150</t>
         </is>
       </c>
+      <c r="K203" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="24" customHeight="1">
       <c r="A204" s="5" t="inlineStr">
@@ -10763,6 +13559,20 @@
           <t>150</t>
         </is>
       </c>
+      <c r="K204" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>54.7</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="24" customHeight="1">
       <c r="A205" s="7" t="inlineStr">
@@ -10803,6 +13613,12 @@
       <c r="H205" s="8" t="inlineStr"/>
       <c r="I205" s="8" t="inlineStr"/>
       <c r="J205" s="8" t="inlineStr"/>
+      <c r="K205" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206" ht="32" customHeight="1">
       <c r="A206" s="5" t="inlineStr">
@@ -10843,6 +13659,20 @@
       <c r="H206" s="6" t="inlineStr"/>
       <c r="I206" s="6" t="inlineStr"/>
       <c r="J206" s="6" t="inlineStr"/>
+      <c r="K206" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="24" customHeight="1">
       <c r="A207" s="7" t="inlineStr">
@@ -10885,6 +13715,20 @@
       <c r="J207" s="8" t="inlineStr">
         <is>
           <t>25</t>
+        </is>
+      </c>
+      <c r="K207" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
